--- a/exports/SBICARD_full_report.xlsx
+++ b/exports/SBICARD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.34</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44588.55208333334</v>
+        <v>44589.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>848.5</v>
+        <v>873.05</v>
       </c>
       <c r="I2" t="n">
         <v>853.1092282227667</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K2" t="n">
-        <v>5.95</v>
+        <v>3.23</v>
       </c>
       <c r="L2" t="n">
         <v>2.31</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>8.69</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44596.55208333334</v>
+        <v>44599.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>855.35</v>
+        <v>839.45</v>
       </c>
       <c r="I3" t="n">
         <v>848.7020632191868</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.03</v>
+        <v>-3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>3.63</v>
+        <v>4.13</v>
       </c>
       <c r="M3" t="n">
         <v>0.84</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>6.83</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44601.38541666666</v>
+        <v>44601.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>852.75</v>
+        <v>864.8</v>
       </c>
       <c r="I4" t="n">
         <v>863.930770488293</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.58</v>
+        <v>-3.02</v>
       </c>
       <c r="L4" t="n">
-        <v>2.45</v>
+        <v>3.21</v>
       </c>
       <c r="M4" t="n">
         <v>0.62</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>6.57</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44610.55208333334</v>
+        <v>44613.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>826.4</v>
+        <v>812.7</v>
       </c>
       <c r="I5" t="n">
         <v>818.860206482631</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.44</v>
+        <v>-6.02</v>
       </c>
       <c r="L5" t="n">
-        <v>5.76</v>
+        <v>6.74</v>
       </c>
       <c r="M5" t="n">
         <v>3.35</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>5.91</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44629.38541666666</v>
+        <v>44629.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>785.1</v>
+        <v>800</v>
       </c>
       <c r="I6" t="n">
         <v>786.1113907265178</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>1.56</v>
       </c>
       <c r="L6" t="n">
         <v>1.69</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.08</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>833.6</v>
+        <v>804.45</v>
       </c>
       <c r="I7" t="n">
         <v>828.4952826472511</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>35</v>
+        <v>39.83333333333334</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L7" t="n">
         <v>2.1</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>6.93</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44678.55208333334</v>
+        <v>44679.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>827.8</v>
+        <v>839.05</v>
       </c>
       <c r="I8" t="n">
         <v>835.7179593721617</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.9</v>
+        <v>-4.3</v>
       </c>
       <c r="L8" t="n">
-        <v>3.34</v>
+        <v>4.61</v>
       </c>
       <c r="M8" t="n">
         <v>1.44</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.48</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>799.45</v>
+        <v>786</v>
       </c>
       <c r="I9" t="n">
         <v>799.1852734077495</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.72</v>
+        <v>-6.32</v>
       </c>
       <c r="L9" t="n">
-        <v>5.13</v>
+        <v>7.31</v>
       </c>
       <c r="M9" t="n">
         <v>-0</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.08</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>766.2</v>
+        <v>774.9</v>
       </c>
       <c r="I10" t="n">
         <v>768.6136269522116</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>2.52</v>
+        <v>1.41</v>
       </c>
       <c r="L10" t="n">
         <v>2.42</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>6.06</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>770</v>
+        <v>744.15</v>
       </c>
       <c r="I11" t="n">
         <v>749.3243887414834</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.63</v>
+        <v>-3.97</v>
       </c>
       <c r="L11" t="n">
-        <v>2.41</v>
+        <v>4.49</v>
       </c>
       <c r="M11" t="n">
-        <v>0.93</v>
+        <v>1.95</v>
       </c>
       <c r="N11" t="n">
-        <v>1.49</v>
+        <v>3.93</v>
       </c>
       <c r="O11" t="n">
         <v>1.16</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.93</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44734.55208333334</v>
+        <v>44735.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>715</v>
+        <v>723.5</v>
       </c>
       <c r="I12" t="n">
         <v>723.2089349860876</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>3.92</v>
+        <v>2.77</v>
       </c>
       <c r="L12" t="n">
         <v>1.7</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44791.55208333334</v>
+        <v>44792.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>957.75</v>
+        <v>941.45</v>
       </c>
       <c r="I13" t="n">
         <v>946.114821686607</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K13" t="n">
-        <v>32.38</v>
+        <v>30.12</v>
       </c>
       <c r="L13" t="n">
         <v>1.72</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.01</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44809.55208333334</v>
+        <v>44810.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>935.8</v>
+        <v>946</v>
       </c>
       <c r="I14" t="n">
         <v>945.8404692250276</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6</v>
+        <v>-0.48</v>
       </c>
       <c r="L14" t="n">
         <v>2.76</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>6.32</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>946</v>
+        <v>925</v>
       </c>
       <c r="I15" t="n">
         <v>925.4336739253265</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-2.22</v>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
         <v>0.72</v>
       </c>
       <c r="N15" t="n">
-        <v>2.44</v>
+        <v>3.12</v>
       </c>
       <c r="O15" t="n">
         <v>1.32</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.92</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44895.38541666666</v>
+        <v>44895.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>820.9</v>
+        <v>824</v>
       </c>
       <c r="I16" t="n">
         <v>821.7914518290896</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>68</v>
+        <v>68.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>11.25</v>
+        <v>10.92</v>
       </c>
       <c r="L16" t="n">
         <v>2.62</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>3.39</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="I17" t="n">
         <v>810.3887029401765</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.21</v>
+        <v>-2.43</v>
       </c>
       <c r="L17" t="n">
-        <v>1.77</v>
+        <v>2.64</v>
       </c>
       <c r="M17" t="n">
         <v>0.02</v>
       </c>
       <c r="N17" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="O17" t="n">
         <v>0.73</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.15</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44959.55208333334</v>
+        <v>44960.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>736</v>
+        <v>748.9</v>
       </c>
       <c r="I18" t="n">
         <v>744.7884067632106</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K18" t="n">
-        <v>8.460000000000001</v>
+        <v>6.85</v>
       </c>
       <c r="L18" t="n">
         <v>1.7</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>7</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>744.45</v>
+        <v>737</v>
       </c>
       <c r="I19" t="n">
         <v>737.9049051727052</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.59</v>
+        <v>-1.59</v>
       </c>
       <c r="L19" t="n">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>4.66</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45016.55208333334</v>
+        <v>45019.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>737</v>
+        <v>743.65</v>
       </c>
       <c r="I20" t="n">
         <v>740.8531594489398</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="L20" t="n">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="M20" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="N20" t="n">
         <v>2.36</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.18</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45096.55208333334</v>
+        <v>45097.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>904.8</v>
+        <v>891.35</v>
       </c>
       <c r="I21" t="n">
         <v>895.3712087441767</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>77.16666666666667</v>
+        <v>78</v>
       </c>
       <c r="K21" t="n">
-        <v>21.67</v>
+        <v>19.86</v>
       </c>
       <c r="L21" t="n">
         <v>1.36</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>104</v>
+        <v>105</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.79</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45126.38541666666</v>
+        <v>45126.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="I22" t="n">
         <v>863.7315679785893</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>4.41</v>
+        <v>2.96</v>
       </c>
       <c r="L22" t="n">
         <v>1.31</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.52</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45156.55208333334</v>
+        <v>45159.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>840.05</v>
+        <v>835</v>
       </c>
       <c r="I23" t="n">
         <v>838.7623084823135</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>30</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.88</v>
+        <v>-3.47</v>
       </c>
       <c r="L23" t="n">
         <v>4.6</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>4.09</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45177.55208333334</v>
+        <v>45180.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>841</v>
+        <v>849.8</v>
       </c>
       <c r="I24" t="n">
         <v>845.3693690395047</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.72</v>
+        <v>-1.77</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>2.39</v>
       </c>
       <c r="M24" t="n">
         <v>0.59</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>3.33</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45187.38541666666</v>
+        <v>45187.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>825.1</v>
+        <v>820</v>
       </c>
       <c r="I25" t="n">
         <v>824.7138055772422</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.91</v>
+        <v>-3.51</v>
       </c>
       <c r="L25" t="n">
-        <v>3.38</v>
+        <v>3.62</v>
       </c>
       <c r="M25" t="n">
         <v>0.12</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>3.94</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45266.55208333334</v>
+        <v>45267.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>748.2</v>
+        <v>769.1</v>
       </c>
       <c r="I26" t="n">
         <v>759.6234905681576</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>79</v>
+        <v>79.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>8.76</v>
+        <v>6.21</v>
       </c>
       <c r="L26" t="n">
         <v>0.68</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>4.7</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45308.55208333334</v>
+        <v>45309.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>753</v>
+        <v>749.3</v>
       </c>
       <c r="I27" t="n">
         <v>752.7246252691519</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.09</v>
+        <v>-2.57</v>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>3.97</v>
       </c>
       <c r="M27" t="n">
         <v>0.4</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>3.04</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45316.38541666666</v>
+        <v>45316.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>748.3</v>
+        <v>761</v>
       </c>
       <c r="I28" t="n">
         <v>755.8255020697831</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>0.13</v>
+        <v>-1.56</v>
       </c>
       <c r="L28" t="n">
-        <v>0.85</v>
+        <v>1.83</v>
       </c>
       <c r="M28" t="n">
         <v>0.6899999999999999</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.76</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45316.55208333334</v>
+        <v>45320.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>761</v>
+        <v>715.2</v>
       </c>
       <c r="I29" t="n">
         <v>717.1537380920154</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>-6.02</v>
       </c>
       <c r="L29" t="n">
-        <v>2.58</v>
+        <v>6.69</v>
       </c>
       <c r="M29" t="n">
-        <v>0.03</v>
+        <v>5.84</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5.89</v>
       </c>
       <c r="O29" t="n">
         <v>2.13</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.53</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45341.55208333334</v>
+        <v>45342.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>730</v>
+        <v>737.75</v>
       </c>
       <c r="I30" t="n">
         <v>733.3962944522791</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.07</v>
+        <v>-3.15</v>
       </c>
       <c r="L30" t="n">
         <v>4.15</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.23</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>716</v>
+        <v>702.6</v>
       </c>
       <c r="I31" t="n">
         <v>715.7159640860948</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.95</v>
+        <v>-4.76</v>
       </c>
       <c r="L31" t="n">
-        <v>3.54</v>
+        <v>5.39</v>
       </c>
       <c r="M31" t="n">
         <v>0.38</v>
       </c>
       <c r="N31" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="O31" t="n">
         <v>1.37</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>4.49</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45386.55208333334</v>
+        <v>45387.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>694.95</v>
+        <v>719.2</v>
       </c>
       <c r="I32" t="n">
         <v>709.0143679176766</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K32" t="n">
-        <v>1.09</v>
+        <v>-2.36</v>
       </c>
       <c r="L32" t="n">
-        <v>1.75</v>
+        <v>2.99</v>
       </c>
       <c r="M32" t="n">
         <v>1.27</v>
       </c>
       <c r="N32" t="n">
-        <v>2.59</v>
+        <v>5.19</v>
       </c>
       <c r="O32" t="n">
         <v>-1.91</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>5.33</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45408.55208333334</v>
+        <v>45411.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>750</v>
+        <v>723.5</v>
       </c>
       <c r="I33" t="n">
         <v>724.2867253391495</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K33" t="n">
-        <v>4.28</v>
+        <v>0.6</v>
       </c>
       <c r="L33" t="n">
         <v>3.63</v>
       </c>
       <c r="M33" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.04</v>
+        <v>3.62</v>
       </c>
       <c r="O33" t="n">
         <v>5.19</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.08</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>715.8</v>
+        <v>717.65</v>
       </c>
       <c r="I34" t="n">
         <v>716.1521392369988</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K34" t="n">
-        <v>1.06</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>2.7</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>5.01</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45474.55208333334</v>
+        <v>45475.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>724.4</v>
+        <v>709.85</v>
       </c>
       <c r="I35" t="n">
         <v>711.9299534870466</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.09</v>
       </c>
       <c r="L35" t="n">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="M35" t="n">
         <v>0.03</v>
       </c>
       <c r="N35" t="n">
-        <v>0.87</v>
+        <v>1.99</v>
       </c>
       <c r="O35" t="n">
         <v>0.27</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>4.75</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45483.38541666666</v>
+        <v>45483.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="I36" t="n">
         <v>735.9513305700015</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.84</v>
+        <v>-4.95</v>
       </c>
       <c r="L36" t="n">
-        <v>4.25</v>
+        <v>5.17</v>
       </c>
       <c r="M36" t="n">
         <v>0.43</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>4.83</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>720.7</v>
+        <v>706.8</v>
       </c>
       <c r="I37" t="n">
         <v>715.6712241368103</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.26</v>
+        <v>-5.13</v>
       </c>
       <c r="L37" t="n">
-        <v>4.48</v>
+        <v>5.74</v>
       </c>
       <c r="M37" t="n">
-        <v>0.63</v>
+        <v>2.46</v>
       </c>
       <c r="N37" t="n">
         <v>1.95</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.36</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45526.55208333334</v>
+        <v>45527.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>714.5</v>
+        <v>717.8</v>
       </c>
       <c r="I38" t="n">
         <v>717.408655898499</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.09</v>
+        <v>-1.56</v>
       </c>
       <c r="L38" t="n">
         <v>2.96</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>3.04</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45559.55208333334</v>
+        <v>45560.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>780.65</v>
+        <v>772.35</v>
       </c>
       <c r="I39" t="n">
         <v>772.4344229808657</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K39" t="n">
-        <v>8.76</v>
+        <v>7.6</v>
       </c>
       <c r="L39" t="n">
         <v>0.53</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.25</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>694.5</v>
+        <v>702.9</v>
       </c>
       <c r="I40" t="n">
         <v>702.8951061135828</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K40" t="n">
-        <v>10.08</v>
+        <v>8.99</v>
       </c>
       <c r="L40" t="n">
         <v>3.84</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>4.89</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45645.38541666666</v>
+        <v>45645.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>703.9</v>
+        <v>703</v>
       </c>
       <c r="I41" t="n">
         <v>703.7691736829014</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K41" t="n">
-        <v>0.14</v>
+        <v>0.01</v>
       </c>
       <c r="L41" t="n">
         <v>1.57</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>3.68</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>676</v>
+        <v>695.7</v>
       </c>
       <c r="I42" t="n">
         <v>690.8367335776107</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>3.84</v>
+        <v>1.04</v>
       </c>
       <c r="L42" t="n">
         <v>0.73</v>
       </c>
       <c r="M42" t="n">
-        <v>0.53</v>
+        <v>0.87</v>
       </c>
       <c r="N42" t="n">
-        <v>1.74</v>
+        <v>3.99</v>
       </c>
       <c r="O42" t="n">
         <v>-1</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>5.5</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>847.55</v>
+        <v>800.9</v>
       </c>
       <c r="I43" t="n">
         <v>835.0869724697058</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>92.16666666666667</v>
+        <v>95</v>
       </c>
       <c r="K43" t="n">
-        <v>21.83</v>
+        <v>15.12</v>
       </c>
       <c r="L43" t="n">
         <v>2.54</v>
       </c>
       <c r="M43" t="n">
-        <v>4.84</v>
+        <v>9.92</v>
       </c>
       <c r="N43" t="n">
-        <v>3.14</v>
+        <v>3.72</v>
       </c>
       <c r="O43" t="n">
         <v>3.99</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>7.59</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>852</v>
+        <v>872.15</v>
       </c>
       <c r="I44" t="n">
         <v>861.691639211282</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.38</v>
+        <v>-8.9</v>
       </c>
       <c r="L44" t="n">
-        <v>6.95</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>0.35</v>
+        <v>1.09</v>
       </c>
       <c r="N44" t="n">
         <v>3.91</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.85</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45771.55208333334</v>
+        <v>45772.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>924</v>
+        <v>870.55</v>
       </c>
       <c r="I45" t="n">
         <v>877.02871351704</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K45" t="n">
-        <v>5.95</v>
+        <v>-0.18</v>
       </c>
       <c r="L45" t="n">
         <v>1.65</v>
       </c>
       <c r="M45" t="n">
-        <v>0.3</v>
+        <v>5.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="O45" t="n">
         <v>3.64</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>8.210000000000001</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45806.55208333334</v>
+        <v>45807.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>911.4</v>
+        <v>927.75</v>
       </c>
       <c r="I46" t="n">
         <v>917.6154285614701</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.69</v>
+        <v>-6.57</v>
       </c>
       <c r="L46" t="n">
-        <v>5.84</v>
+        <v>6.71</v>
       </c>
       <c r="M46" t="n">
         <v>3.89</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.03</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45826.55208333334</v>
+        <v>45827.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>970.05</v>
+        <v>944.6</v>
       </c>
       <c r="I47" t="n">
         <v>968.4346900437232</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>4.56</v>
+        <v>1.82</v>
       </c>
       <c r="L47" t="n">
         <v>2.02</v>
@@ -3120,7 +3683,7 @@
         <v>2.3</v>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O47" t="n">
         <v>0.92</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.45</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>812.6</v>
+        <v>818.45</v>
       </c>
       <c r="I48" t="n">
         <v>817.7031888462611</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K48" t="n">
-        <v>13.97</v>
+        <v>13.35</v>
       </c>
       <c r="L48" t="n">
         <v>7.45</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>4.62</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>801.2</v>
+        <v>798.25</v>
       </c>
       <c r="I49" t="n">
         <v>798.6961669515721</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.11</v>
+        <v>-2.47</v>
       </c>
       <c r="L49" t="n">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="M49" t="n">
         <v>0.75</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>4.55</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>821</v>
+        <v>843.25</v>
       </c>
       <c r="I50" t="n">
         <v>823.1642256945094</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.85</v>
+        <v>-5.64</v>
       </c>
       <c r="L50" t="n">
-        <v>2.85</v>
+        <v>5.86</v>
       </c>
       <c r="M50" t="n">
         <v>2.27</v>
       </c>
       <c r="N50" t="n">
-        <v>2.18</v>
+        <v>4.75</v>
       </c>
       <c r="O50" t="n">
         <v>-2.06</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>5.32</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45954.55208333334</v>
+        <v>45957.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>936.45</v>
+        <v>904.65</v>
       </c>
       <c r="I51" t="n">
         <v>905.3962269617473</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K51" t="n">
-        <v>11.05</v>
+        <v>7.28</v>
       </c>
       <c r="L51" t="n">
         <v>2.4</v>
       </c>
       <c r="M51" t="n">
-        <v>0.77</v>
+        <v>3.36</v>
       </c>
       <c r="N51" t="n">
-        <v>1.49</v>
+        <v>4.11</v>
       </c>
       <c r="O51" t="n">
         <v>4.75</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.63</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46010.38541666666</v>
+        <v>46010.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>856.7</v>
+        <v>870.6</v>
       </c>
       <c r="I52" t="n">
         <v>868.1535811416205</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K52" t="n">
-        <v>5.3</v>
+        <v>3.76</v>
       </c>
       <c r="L52" t="n">
         <v>1.14</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,25 +4076,25 @@
         <v>4.9</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46020.55208333334</v>
+        <v>46021.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>851.3</v>
+        <v>835.45</v>
       </c>
       <c r="I53" t="n">
         <v>836.296931909516</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.22</v>
+        <v>-4.04</v>
       </c>
       <c r="L53" t="n">
-        <v>2.72</v>
+        <v>4.7</v>
       </c>
       <c r="M53" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="N53" t="n">
         <v>1.58</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>5.32</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>873.45</v>
+        <v>886.75</v>
       </c>
       <c r="I54" t="n">
         <v>879.8663691163406</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.55</v>
+        <v>-6.14</v>
       </c>
       <c r="L54" t="n">
-        <v>5.49</v>
+        <v>6.67</v>
       </c>
       <c r="M54" t="n">
         <v>0.34</v>
       </c>
       <c r="N54" t="n">
-        <v>1.89</v>
+        <v>2.58</v>
       </c>
       <c r="O54" t="n">
         <v>-0.62</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,25 +4214,25 @@
         <v>4.69</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>865</v>
+        <v>853.5</v>
       </c>
       <c r="I55" t="n">
         <v>854.3689874973267</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.45</v>
+        <v>-3.75</v>
       </c>
       <c r="L55" t="n">
-        <v>2.98</v>
+        <v>5.49</v>
       </c>
       <c r="M55" t="n">
-        <v>0.74</v>
+        <v>1.27</v>
       </c>
       <c r="N55" t="n">
         <v>1.4</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.11</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46070.55208333334</v>
+        <v>46071.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>775</v>
+        <v>787.05</v>
       </c>
       <c r="I56" t="n">
         <v>782.9922087595415</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K56" t="n">
-        <v>9.199999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.38</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>782.6</v>
+        <v>746.85</v>
       </c>
       <c r="I57" t="n">
         <v>759.2090209346219</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.57</v>
+        <v>-5.11</v>
       </c>
       <c r="L57" t="n">
-        <v>3.43</v>
+        <v>5.34</v>
       </c>
       <c r="M57" t="n">
-        <v>0.63</v>
+        <v>4.17</v>
       </c>
       <c r="N57" t="n">
-        <v>1.62</v>
+        <v>4.17</v>
       </c>
       <c r="O57" t="n">
         <v>1.68</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.41</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46125.55208333334</v>
+        <v>46127.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>672.2</v>
+        <v>684.5</v>
       </c>
       <c r="I58" t="n">
         <v>681.5021061702791</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K58" t="n">
-        <v>10</v>
+        <v>8.35</v>
       </c>
       <c r="L58" t="n">
         <v>2.48</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>6.25</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46140.38541666666</v>
+        <v>46140.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>659.5</v>
+        <v>647.8</v>
       </c>
       <c r="I59" t="n">
         <v>654.0176226441545</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.65</v>
+        <v>-5.36</v>
       </c>
       <c r="L59" t="n">
-        <v>4.85</v>
+        <v>5.61</v>
       </c>
       <c r="M59" t="n">
         <v>2.6</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,25 +4559,25 @@
         <v>7.21</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>587</v>
+        <v>610.4</v>
       </c>
       <c r="I60" t="n">
         <v>594.8433567957244</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>45</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>9.390000000000001</v>
+        <v>5.77</v>
       </c>
       <c r="L60" t="n">
         <v>2.05</v>
       </c>
       <c r="M60" t="n">
-        <v>1.24</v>
+        <v>1.87</v>
       </c>
       <c r="N60" t="n">
         <v>3.15</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.51</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46202.55208333334</v>
+        <v>46203.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>600.95</v>
+        <v>596.85</v>
       </c>
       <c r="I61" t="n">
         <v>598.7771972890885</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.55</v>
+        <v>-2.22</v>
       </c>
       <c r="L61" t="n">
-        <v>2.2</v>
+        <v>2.89</v>
       </c>
       <c r="M61" t="n">
         <v>0.31</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>7.07</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46213.55208333334</v>
+        <v>46216.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>611.5</v>
+        <v>616.5</v>
       </c>
       <c r="I62" t="n">
         <v>614.6345627838728</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.45</v>
+        <v>-3.29</v>
       </c>
       <c r="L62" t="n">
-        <v>2.96</v>
+        <v>3.79</v>
       </c>
       <c r="M62" t="n">
         <v>0.9399999999999999</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.14</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46248.38541666666</v>
+        <v>46248.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>639.25</v>
+        <v>630.2</v>
       </c>
       <c r="I63" t="n">
         <v>637.671924247097</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>32</v>
+        <v>32.16666666666666</v>
       </c>
       <c r="K63" t="n">
-        <v>3.69</v>
+        <v>2.22</v>
       </c>
       <c r="L63" t="n">
         <v>2.26</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.08</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46253.55208333334</v>
+        <v>46254.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>625.65</v>
+        <v>648.6</v>
       </c>
       <c r="I64" t="n">
         <v>648.1773375962817</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>5</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>0.72</v>
+        <v>-2.92</v>
       </c>
       <c r="L64" t="n">
-        <v>2.05</v>
+        <v>3.83</v>
       </c>
       <c r="M64" t="n">
         <v>0.5</v>
       </c>
       <c r="N64" t="n">
-        <v>1.9</v>
+        <v>3.49</v>
       </c>
       <c r="O64" t="n">
         <v>-1.68</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.87</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46266.38541666666</v>
+        <v>46266.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>637.4</v>
+        <v>632.05</v>
       </c>
       <c r="I65" t="n">
         <v>632.2981030742081</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.73</v>
+        <v>-2.55</v>
       </c>
       <c r="L65" t="n">
         <v>3.37</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,14 @@
       <c r="Q66" t="n">
         <v>75</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6308,7 +7107,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.1</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6">
@@ -6318,7 +7117,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.6</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="7">
@@ -6328,7 +7127,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>92.2</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8">
@@ -6338,7 +7137,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="9">
@@ -6348,7 +7147,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.3</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="10">
@@ -6358,7 +7157,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55.9</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="11">
@@ -6368,7 +7167,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -6378,7 +7177,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -6388,7 +7187,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.8</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="14">
@@ -6398,7 +7197,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.49</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="15">
@@ -6408,7 +7207,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.42</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16">
@@ -6418,7 +7217,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.56</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="17">
@@ -6428,7 +7227,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.38</v>
+        <v>30.12</v>
       </c>
     </row>
     <row r="18">
@@ -6438,7 +7237,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="19">
@@ -6448,7 +7247,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.78</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
@@ -6458,7 +7257,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -6468,7 +7267,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.45</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -6478,7 +7277,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -6498,7 +7297,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.34</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="25">
@@ -6518,7 +7317,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="27">
@@ -6528,7 +7327,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.35</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="28">
@@ -6538,7 +7337,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
